--- a/Översikt SKINNSKATTEBERG.xlsx
+++ b/Översikt SKINNSKATTEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45343</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45450</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>46009</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>46253</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>44515</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>44908</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46150</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45974</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45537</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45770</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>45390</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>45425</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>46150</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45985</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45574</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>46254</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>45537</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>45755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>44829</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>45385</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45232</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>45246</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45428</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>46140</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45931</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>46150</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45980</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>46170</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>46174</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>46185</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>45359</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>46107</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45568</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45519</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>44995</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>46210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>45359</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45322</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46261</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>45099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>46268</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>46279</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45832</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45548</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45832</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>46107</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44789</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44545</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44879</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44466</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44674</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44829</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44545</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>44741</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>44823</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>44544</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44529</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44529</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44519</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44545</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>44852</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>44544</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>44852</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>44491</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>45174</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>44728</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45097</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45762</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>45058</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>45435</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>45237</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>45604</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45425</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44728</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45244</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>45406</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44768</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>45609</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>45111</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>45506</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44910</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45420</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>45637</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>45216</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44974</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>44468</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44468</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45250</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>45375</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45434</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>45247</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45610</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>45162</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>44935</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45686</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45770</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>45571</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>45406</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>45532</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44859</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45527</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45245</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>44603</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>45198</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44964</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>44993</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45617</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45754</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45447</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>45198</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45063</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>45063</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45534</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45114</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45890</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45571</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>45571</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>45237</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>45434</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>45617</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>45897</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>45897</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45897</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>45897</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45897</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>45897</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>46136</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45410</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>45134</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>45586</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>45096</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>45740</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45910</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45910</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>45407</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>46141</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>46140</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>46140</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45910</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45915</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45915</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45376</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>45901</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44974</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45919</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45919</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45919</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45068</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45090</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45329</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45931</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>45931</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>46142</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>46142</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>46142</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>46142</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>46142</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>46142</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44903</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>46142</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44648</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>44936</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>45945</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45947</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45947</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45947</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45947</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45537</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45952</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45959</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45958</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>46150</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45177</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>45960</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>46150</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>45965</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>44475</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45967</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>44469</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>44466</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44468</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45967</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45420</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>45967</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>45973</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>44462</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45973</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>45531</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45973</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44468</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45975</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45979</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>46154</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45512</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>46157</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45604</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45771</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45987</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45407</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45992</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45992</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>46163</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44803</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>46163</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>46163</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>46163</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>46163</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45429</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46003</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>46009</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45901</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>46009</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45054</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45056</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45390</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>46170</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>46170</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>46170</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45447</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45485</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>45555</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>46170</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>46170</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45387</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45063</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45401</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45156</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>46037</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>46037</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>45096</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>46051</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>46051</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>46051</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>45170</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45558</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>46056</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>46177</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>46178</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45720</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>46178</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>46177</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>46178</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>46182</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45574</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45574</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>46182</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45082</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>44498</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45128</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>46185</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45169</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>46185</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>45554</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>46185</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45085</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45617</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>46190</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>46190</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44965</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>45114</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>46190</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>46191</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>46191</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>46195</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45006</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>46105</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>45385</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46107</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45401</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>46197</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>46197</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>45393</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45686</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>46108</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>46107</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44967</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>46197</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>46108</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>46107</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45568</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46111</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>46244</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>46111</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>45643</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>46111</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45435</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>44995</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>46114</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>46199</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>44806</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>46244</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>46200</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>46119</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44883</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>46244</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>46244</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>46200</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>46122</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>46199</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45554</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>44519</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>46129</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45156</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>45252</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45504</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>46134</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>46134</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>46134</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45306</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45306</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45306</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45170</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>46247</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45744</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>46248</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45174</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46210</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45555</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45180</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45264</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45520</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>44713</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>46253</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>45532</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>45532</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45554</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>45048</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45532</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45114</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46260</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45506</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>46260</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>46262</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46262</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>46262</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>46262</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45407</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>46265</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>45170</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>45252</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>45014</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>45014</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45762</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>45040</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45592</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>46268</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45777</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45777</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>46199</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>46274</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45377</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45541</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44867</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>46279</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45547</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46237</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45480</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>46262</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>46237</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45786</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>46282</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45443</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45527</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45476</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>46282</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45804</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45480</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>45820</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45820</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45825</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45825</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45827</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45827</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45832</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45832</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>45832</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45848</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45853</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45554</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45853</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>45880</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45435</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45786</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45827</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>45853</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>45897</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45897</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45897</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45901</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45915</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>46147</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>46182</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>46199</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>46260</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>46262</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>

--- a/Översikt SKINNSKATTEBERG.xlsx
+++ b/Översikt SKINNSKATTEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45343</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45450</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>46253</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>44515</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>46150</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44908</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45974</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>45537</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46289</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45425</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45985</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45770</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>46150</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45390</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>46289</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>46289</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45537</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>46289</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>45762</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45755</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>44829</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45322</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>45385</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>45359</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45232</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>46107</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45980</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>46140</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>46150</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45568</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>46170</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45519</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>46174</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44995</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45428</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>46210</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>46261</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>46268</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>46279</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>46285</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>46285</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45099</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45246</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>45548</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>46107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44466</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44674</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44829</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44531</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>44545</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44741</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44823</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44544</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44529</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44519</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44545</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44544</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44852</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>44491</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>45329</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>45198</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>45532</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>45082</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>45434</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45244</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>45435</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45435</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>44806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>45447</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45410</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>45786</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45443</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45097</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>44468</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>45247</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>45476</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45527</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>45574</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>45574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>46037</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44475</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45890</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>46037</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45897</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45897</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45897</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45897</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45897</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45054</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46051</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>46051</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>46051</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45910</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>45406</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>46056</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>45910</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45554</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45216</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>45915</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>45915</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>45506</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>45901</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45554</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45919</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45504</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45555</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>45804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>45919</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>45919</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>45919</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44967</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45931</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45931</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45252</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>44974</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45156</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45945</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45947</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>45947</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45947</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>46105</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45558</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>46107</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>46107</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>46107</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>46108</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>46108</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>46111</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>46111</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>46111</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>46114</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45960</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>46119</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45744</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45959</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45609</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>46122</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45965</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>45604</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>45967</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45967</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45967</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45480</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45973</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>45973</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>45973</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45973</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>45975</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44993</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45162</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>46129</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45610</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45979</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>46134</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>46134</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>46134</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45537</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45177</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>46136</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45987</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>45771</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44728</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>44768</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45992</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45992</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>45531</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45534</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>46140</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>46140</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>46003</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45754</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45447</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>45820</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44648</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45901</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>45820</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>46009</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>46009</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45485</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45617</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45686</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45825</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45825</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45720</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>46142</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45827</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45827</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>46141</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45586</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>46142</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>46142</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46142</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>46142</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>46142</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>46142</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>44468</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>46150</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>46150</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>45832</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45832</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>44466</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45406</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>45832</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>45264</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>46154</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45063</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>46157</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44903</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45555</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>45128</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>46163</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>46163</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>46163</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>46163</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>46163</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45848</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45554</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45853</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45853</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45375</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>44965</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45568</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>46170</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>46170</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>46170</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>46170</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>44936</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46170</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45527</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45434</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46177</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>46177</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>46178</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>46178</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>46178</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45429</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>46182</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>46182</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44519</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>46185</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>46185</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>46185</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>44995</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45180</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45401</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45420</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>46191</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>46190</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>46190</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>46191</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45014</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45014</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>46190</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45643</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46195</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>46197</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46197</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45198</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45686</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>46197</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>45393</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>46200</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45880</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>46199</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46200</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>46199</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45407</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45170</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45114</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>45770</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>46210</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>46253</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45174</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45085</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45245</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>46260</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44728</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>46260</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>46262</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>46262</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>46262</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>46262</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45407</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45096</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45174</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45169</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45420</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45407</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>46265</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45170</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45306</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45306</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45306</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>46268</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45237</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>44974</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>46274</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>46199</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44498</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45532</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45532</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45063</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45063</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>46237</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>46237</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>46279</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>45532</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>46282</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>46262</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>44859</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>46282</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44468</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44468</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>46285</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45040</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45376</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>45058</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>46244</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>46244</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>46244</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>45048</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>46244</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>45250</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>46247</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>46290</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>46289</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>46248</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>46290</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>46290</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44603</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>45425</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45111</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45252</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45387</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45114</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>44964</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45390</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>44469</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45090</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45762</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>45762</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45637</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45006</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45056</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45520</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44883</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>44803</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44910</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45134</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45401</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>45114</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45068</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>44713</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>45592</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45571</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31596,7 +31596,7 @@
         <v>45571</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>45617</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45506</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>45170</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45604</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44935</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>45237</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>45156</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>45385</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45571</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45740</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45096</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>45554</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45617</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>45777</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45777</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44867</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45377</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45541</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45547</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45480</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45435</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45786</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45827</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>45853</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45897</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45897</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45897</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45901</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45915</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>46147</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>46182</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>46199</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>46260</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>46262</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>46290</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>

--- a/Översikt SKINNSKATTEBERG.xlsx
+++ b/Översikt SKINNSKATTEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45343</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45450</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>46253</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>44515</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>46150</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44908</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45974</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>46254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>45537</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46289</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45425</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45985</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45770</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>46150</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45390</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>46289</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>46289</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45537</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>46289</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>45762</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45755</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>44829</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45322</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>45385</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>45359</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45232</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>46107</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45980</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>46140</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>46150</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45568</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>46170</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45519</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>46174</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44995</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45428</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>46210</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>46261</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>46268</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>46279</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>46285</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>46285</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45099</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45246</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>45548</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>46107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44466</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44674</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44829</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44531</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>44545</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44741</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44823</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44544</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44529</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44519</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44545</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44544</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44852</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>44491</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>45329</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>45198</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>45532</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>45082</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>45434</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45244</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>45435</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45435</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>44806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>45447</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45410</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>45786</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45443</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45097</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>44468</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>45247</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>45476</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45527</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>45574</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>45574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>46037</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44475</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45890</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>46037</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45897</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45897</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45897</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45897</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45897</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45054</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46051</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>46051</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>46051</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45910</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>45406</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>46056</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>45910</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45554</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45216</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>45915</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>45915</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>45506</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>45901</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45554</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45919</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45504</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45555</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>45804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>45919</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>45919</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>45919</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44967</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45931</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45931</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45252</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>44974</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45156</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45945</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45947</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>45947</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45947</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>46105</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45558</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>46107</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>46107</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>46107</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>46108</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>46108</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>46111</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>46111</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>46111</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>46114</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45960</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>46119</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45744</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45959</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45609</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>46122</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45965</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>45604</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>45967</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45967</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45967</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45480</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45973</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>45973</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>45973</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45973</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>45975</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44993</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45162</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>46129</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45610</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45979</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>46134</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>46134</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>46134</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45537</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45177</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>46136</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45987</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>45771</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44728</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>44768</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45992</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45992</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>45531</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45534</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>46140</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>46140</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>46003</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45754</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45447</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>45820</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44648</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45901</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>45820</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>46009</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>46009</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45485</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45617</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45686</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45825</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45825</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45720</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>46142</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45827</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45827</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>46141</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45586</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>46142</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>46142</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46142</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>46142</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>46142</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>46142</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>44468</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>46150</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>46150</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>45832</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45832</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>44466</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45406</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>45832</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>45264</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>46154</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45063</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>46157</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44903</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45555</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>45128</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>46163</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>46163</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>46163</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>46163</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>46163</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45848</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45554</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45853</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45853</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45375</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>44965</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45568</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>46170</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>46170</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>46170</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>46170</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>44936</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46170</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45527</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45434</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46177</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>46177</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>46178</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>46178</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>46178</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45429</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>46182</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>46182</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44519</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>46185</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>46185</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>46185</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>44995</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45180</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45401</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45420</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>46191</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>46190</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>46190</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>46191</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45014</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45014</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>46190</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45643</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46195</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>46197</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46197</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45198</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45686</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>46197</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>45393</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>46200</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45880</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>46199</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46200</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>46199</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45407</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45170</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45114</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>45770</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>46210</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>46253</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45174</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45085</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45245</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>46260</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44728</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>46260</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>46262</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>46262</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>46262</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>46262</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45407</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45096</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45174</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45169</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45420</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45407</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>46265</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45170</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45306</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45306</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45306</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>46268</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45237</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>44974</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>46274</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>46199</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44498</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45532</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45532</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45063</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45063</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>46237</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>46237</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>46279</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>45532</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>46282</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>46262</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>44859</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>46282</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44468</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44468</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>46285</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45040</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45376</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>45058</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>46244</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>46244</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>46244</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>45048</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>46244</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>45250</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>46247</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>46290</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>46289</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>46248</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>46290</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>46290</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44603</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>45425</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45111</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45252</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45387</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45114</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>44964</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45390</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>44469</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45090</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45762</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>45762</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45637</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45006</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45056</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45520</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44883</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>44803</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44910</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45134</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45401</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>45114</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45068</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>44713</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>45592</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45571</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31596,7 +31596,7 @@
         <v>45571</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>45617</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45506</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>45170</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45604</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44935</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>45237</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>45156</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>45385</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45571</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45740</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45096</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>45554</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45617</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>45777</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45777</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44867</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45377</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45541</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45547</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45480</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45435</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45786</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45827</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>45853</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45897</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45897</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45897</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45901</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45915</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>46147</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>46182</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>46199</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>46260</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>46262</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>46290</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>

--- a/Översikt SKINNSKATTEBERG.xlsx
+++ b/Översikt SKINNSKATTEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45343</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45450</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>46253</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>44515</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44908</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45974</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45537</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>46254</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45770</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45390</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45985</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>45425</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>46150</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>45574</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>46289</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>46289</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45755</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45537</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>45762</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>44829</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45385</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45931</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45232</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45246</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>46107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45980</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>45596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>45832</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45428</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>46140</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>46150</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>46170</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>46174</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>46185</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>45474</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>46210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>46261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>46268</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>46279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45359</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>46285</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>46285</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45568</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45078</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45519</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44995</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45359</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45322</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45099</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>45548</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>46107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44674</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44829</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44531</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>44545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>44741</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44823</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44544</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44529</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44529</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44519</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44852</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44544</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44852</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>45174</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44728</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>45097</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45058</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45435</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45604</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>45237</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45425</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>45609</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>45111</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45547</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>46003</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45480</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>44768</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45244</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>45406</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>46009</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>45901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>46009</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45506</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45890</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>44910</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45420</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45897</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45897</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>45897</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45897</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45897</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>45637</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45216</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44974</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>46037</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46037</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>45375</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45786</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45250</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45434</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45910</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>45910</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>45443</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>45910</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>45527</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45915</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45915</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45247</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45901</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>45476</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>46051</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45919</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>45919</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45919</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>46051</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45919</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>46051</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45804</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>45162</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45610</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>46056</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45686</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45931</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45931</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44935</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45770</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45571</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45532</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45406</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45945</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45947</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>45947</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44859</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45947</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45947</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45952</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>45959</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45960</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>45527</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45245</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>45965</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>44603</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45480</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>45967</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45198</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45967</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45967</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>44964</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>44993</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45973</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45973</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45973</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45973</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45975</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>46105</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45979</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>46107</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>46108</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>46107</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>46108</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46107</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>46111</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>46111</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>45820</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>46111</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45771</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>46114</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45987</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45825</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45617</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>46119</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45754</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45825</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>46122</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45992</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45992</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45198</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>46129</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45827</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45063</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45063</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45832</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45832</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>45114</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45832</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>46134</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>46134</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>46134</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45571</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>45571</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45237</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45434</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45410</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45447</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45134</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45096</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>45848</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45740</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45407</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45376</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         <v>45534</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>45853</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45554</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45853</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44974</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45068</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45090</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45617</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>46136</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45329</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>44903</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>45586</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44648</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>46141</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>46140</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>46140</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>44936</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>45537</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>46142</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>46142</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>46142</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>46142</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>46142</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>46142</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>46142</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45177</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>46150</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46150</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44475</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>46154</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45420</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>46157</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45531</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>46163</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>46163</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>46163</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>46163</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>46163</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45512</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>45880</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45604</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>46170</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>46170</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>46170</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>46170</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>46170</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45407</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>46177</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>44803</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>46178</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>46178</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>46177</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>46178</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>46182</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>46182</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46185</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>46185</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>46185</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45429</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>46190</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46190</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>46190</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>46191</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>46191</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45054</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>46195</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45056</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>46197</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>46197</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45393</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45686</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45390</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>46199</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>46200</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46200</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>46199</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>45447</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45485</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45555</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45387</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45063</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45401</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45156</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>46210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>45096</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>46260</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45170</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>46260</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>46262</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>46262</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45558</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>46262</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>46262</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45407</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>46265</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>45720</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45574</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45574</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>46268</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>46199</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45082</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>46274</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44498</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45128</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>46279</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45169</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>46237</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>46262</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45554</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45617</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44965</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45114</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>46282</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>46282</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45006</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45385</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45401</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46244</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>46244</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>46244</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>46244</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>44967</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>46285</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>45568</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45643</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45435</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>44995</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44806</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>46289</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44883</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45554</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44519</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45156</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>46290</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>46290</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>46247</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45252</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>45504</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>46290</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>46248</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45306</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45306</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45306</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>46237</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>46253</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45744</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>45174</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45555</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45180</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45264</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45520</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>44713</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>45532</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45532</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45554</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45048</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45532</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>45114</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45506</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>45170</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45252</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45014</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45014</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>45762</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>45040</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45592</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45777</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>45777</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>45377</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45541</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44867</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45435</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45786</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45827</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45853</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45897</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>45897</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45897</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>45901</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>45915</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>46147</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>46182</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>46199</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>46260</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>46262</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>46290</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>

--- a/Översikt SKINNSKATTEBERG.xlsx
+++ b/Översikt SKINNSKATTEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45343</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45450</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>46253</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>44515</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44908</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45974</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45537</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>46254</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45770</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45390</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45985</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>45425</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>46150</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>45574</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>46289</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>46289</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45755</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45537</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>45762</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>44829</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45385</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45931</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45232</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>45246</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>46107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45980</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>45596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>45832</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45428</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>46140</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>46150</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>46170</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>46174</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>46185</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>45474</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>46210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>46261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>46268</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>46279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45359</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>46285</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>46285</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45568</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45078</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45519</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44995</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45359</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45322</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45099</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>45548</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>46107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44674</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44829</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44531</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>44545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>44741</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44823</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44544</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44529</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44529</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44519</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44852</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44544</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44852</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>45174</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44728</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>45097</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45058</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45435</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45604</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>45237</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45425</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>45609</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>45111</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45547</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>46003</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45480</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>44768</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45244</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>45406</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>46009</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>45901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>46009</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45506</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45890</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>44910</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45420</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45897</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45897</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>45897</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45897</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45897</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>45637</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45216</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44974</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>46037</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46037</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>45375</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45786</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45250</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45434</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45910</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>45910</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>45443</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>45910</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>45527</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45915</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45915</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45247</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45901</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>45476</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>46051</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45919</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>45919</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45919</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>46051</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45919</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>46051</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45804</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>45162</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45610</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>46056</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45686</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45931</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45931</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44935</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45770</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45571</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45532</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45406</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45945</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45947</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>45947</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44859</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45947</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45947</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45952</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>45959</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45960</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>45527</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45245</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>45965</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>44603</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45480</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>45967</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45198</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45967</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45967</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>44964</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>44993</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45973</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45973</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45973</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45973</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45975</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>46105</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45979</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>46107</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>46108</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>46107</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>46108</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46107</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>46111</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>46111</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>45820</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>46111</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45771</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>46114</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45987</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45825</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45617</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>46119</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45754</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45825</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>46122</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45992</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45992</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45198</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>46129</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45827</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45063</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45063</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45832</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45832</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>45114</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45832</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>46134</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>46134</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>46134</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45571</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>45571</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45237</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45434</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45410</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45447</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45134</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45096</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>45848</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45740</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45407</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45376</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         <v>45534</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>45853</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45554</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45853</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44974</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45068</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45090</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45617</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>46136</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45329</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>44903</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>45586</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44648</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>46141</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>46140</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>46140</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>44936</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>45537</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>46142</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>46142</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>46142</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>46142</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>46142</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>46142</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>46142</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45177</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>46150</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46150</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44475</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>46154</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45420</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>46157</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45531</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>46163</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>46163</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>46163</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>46163</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>46163</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45512</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>45880</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45604</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>46170</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>46170</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>46170</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>46170</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>46170</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45407</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>46177</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>44803</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>46178</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>46178</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>46177</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>46178</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>46182</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>46182</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46185</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>46185</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>46185</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45429</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>46190</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46190</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>46190</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>46191</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>46191</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45054</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>46195</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45056</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>46197</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>46197</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45393</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45686</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45390</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>46199</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>46200</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46200</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>46199</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>45447</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45485</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45555</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45387</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45063</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45401</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45156</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>46210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>45096</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>46260</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45170</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>46260</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>46262</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>46262</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45558</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>46262</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>46262</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45407</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>46265</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>45720</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45574</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45574</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>46268</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>46199</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45082</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>46274</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44498</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45128</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>46279</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45169</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>46237</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>46262</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45554</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45617</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44965</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45114</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>46282</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>46282</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45006</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45385</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45401</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46244</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>46244</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>46244</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>46244</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>44967</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>46285</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>45568</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45643</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45435</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>44995</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44806</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>46289</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44883</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45554</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44519</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45156</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>46290</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>46290</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>46247</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45252</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>45504</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>46290</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>46248</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45306</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45306</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45306</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>46237</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>46253</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45744</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>45174</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45555</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45180</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45264</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45520</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>44713</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>45532</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45532</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45554</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45048</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45532</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>45114</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45506</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>45170</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45252</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45014</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45014</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>45762</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>45040</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45592</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45777</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>45777</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>45377</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45541</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44867</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45435</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45786</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45827</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45853</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45897</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>45897</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45897</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>45901</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>45915</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>46147</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>46182</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>46199</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>46260</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>46262</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>46290</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>

--- a/Översikt SKINNSKATTEBERG.xlsx
+++ b/Översikt SKINNSKATTEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45343</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45450</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>46253</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>44515</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44908</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45974</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45537</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>46254</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45425</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45390</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>45770</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>46150</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>46289</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>46289</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45762</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45755</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45537</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>46289</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45385</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>45078</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44829</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>45596</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45322</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45359</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45568</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>45474</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45519</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44995</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>45428</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>45359</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45232</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>46107</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45099</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45246</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>46140</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46150</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>46170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>46174</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>46185</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>46268</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>46279</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46285</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46285</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>46261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45931</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>45548</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>46107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44674</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44829</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44531</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>44545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>44544</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44741</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44852</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44544</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44529</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>44519</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44545</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>45637</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>45434</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>45406</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>45006</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45264</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>45056</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45244</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45520</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45435</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45435</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44883</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45063</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>45329</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>44803</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44910</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44903</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>45134</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45401</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>45114</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45198</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45068</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>44713</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>45512</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45592</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45410</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45555</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44806</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45571</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45571</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45617</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45532</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45447</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45128</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45506</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45170</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>45082</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45604</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45375</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>44965</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>44935</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45568</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>45097</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45237</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45247</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45156</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45527</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45434</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45890</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45897</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45897</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>45897</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>45897</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45897</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45385</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45897</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45571</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>45740</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>45574</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45574</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>45096</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45554</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45617</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45910</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45910</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>45777</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>45777</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45054</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45429</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45915</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45915</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44867</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45901</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44519</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45377</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45541</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45406</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45554</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45216</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44995</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>45506</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>45919</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45554</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>45919</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>45919</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45180</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>45919</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45401</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45420</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>45504</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>45555</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45014</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45014</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>45547</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45643</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45480</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45198</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45786</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>45443</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45476</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44967</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45527</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45252</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45931</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45931</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44974</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45407</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45170</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45804</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45114</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45156</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>45558</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45770</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45480</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45947</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45947</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>45947</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45947</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45820</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45820</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45744</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>45609</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>45174</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45825</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45825</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45085</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45604</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45827</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45245</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>45832</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45832</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45952</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45958</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45960</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45959</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45832</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44993</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45162</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45610</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45965</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45407</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>45096</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45174</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45537</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45169</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45967</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45967</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45967</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45420</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45177</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>44728</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>44768</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45848</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45973</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45554</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45973</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45973</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45973</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45853</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45531</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45853</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45170</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45306</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45306</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45306</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45975</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45237</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44974</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45754</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45979</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>44648</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45485</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>44498</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45880</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45532</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45532</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45063</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45063</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45686</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45720</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45532</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>46105</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>46107</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>46107</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>46107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>44859</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>46108</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45987</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>46108</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>46111</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45771</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45992</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45992</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>46111</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>46111</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>46114</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>46119</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>46122</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45040</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45376</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>46129</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>45058</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>46003</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>46134</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>46134</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>46134</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45048</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45250</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45901</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>46136</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>46009</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>46009</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>44603</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45425</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>45534</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>46140</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46140</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45447</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45111</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45252</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45387</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46037</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>46037</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45114</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>44964</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45390</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45090</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45762</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45617</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45762</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>46142</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>46051</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>46051</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>46051</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>46141</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>46056</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45586</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>46142</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>46142</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>46142</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>46142</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46142</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>46142</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>46150</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>46150</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46154</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>46157</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>46163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>46163</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>46163</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>46163</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>46163</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>46170</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>46170</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>46170</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>46170</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>46170</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>46177</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>46177</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>46178</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>46178</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>46178</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>46182</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>46182</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>46185</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>46185</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>46185</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>46191</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>46190</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>46190</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>46191</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>46190</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>46195</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46197</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>46197</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45686</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>46197</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45393</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>46200</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>46199</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>46200</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>46199</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>46210</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45407</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>46265</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>46268</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46274</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>46199</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>46237</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>46279</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>46282</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>46282</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>46285</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>46244</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>46244</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>46244</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>46244</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>46247</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>46290</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>46289</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>46290</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>46290</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>46290</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>46248</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>46237</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>46253</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>46300</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>46302</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46262</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>46262</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32253,7 +32253,7 @@
         <v>46262</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>46262</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>46262</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>46260</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>46260</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>45435</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45786</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45827</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45853</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45897</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45897</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>45897</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45901</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45915</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>46147</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>46182</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>46199</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>46290</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>46260</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>46262</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>

--- a/Översikt SKINNSKATTEBERG.xlsx
+++ b/Översikt SKINNSKATTEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45343</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45450</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>46253</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>44515</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44908</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45974</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>45537</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>46254</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45425</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45390</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>45770</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>46150</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>46289</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>46289</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45762</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45755</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45537</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>46289</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45385</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>45078</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44829</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>45596</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45322</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45359</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45568</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>45474</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45519</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44995</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>45428</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>45359</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45232</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>46107</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45099</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45246</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>46140</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46150</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>46170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>46174</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>46185</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>46268</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>46279</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46285</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46285</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>46261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45931</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>45548</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>46107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44674</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44829</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44531</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>44545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>44544</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44741</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44852</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44544</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44529</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>44519</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44545</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>45637</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>45434</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>45406</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>45006</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45264</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>45056</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45244</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45520</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45435</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45435</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44883</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45063</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>45329</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>44803</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44910</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44903</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>45134</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45401</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>45114</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45198</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45068</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>44713</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>45512</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45592</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45410</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45555</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44806</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45571</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45571</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45617</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45532</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45447</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45128</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45506</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45170</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>45082</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45604</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45375</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>44965</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>44935</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45568</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>45097</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45237</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45247</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45156</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45527</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45434</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45890</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45897</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45897</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>45897</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>45897</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45897</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45385</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45897</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45571</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>45740</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>45574</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45574</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>45096</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45554</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45617</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45910</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45910</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>45777</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>45777</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45054</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45429</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45915</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45915</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44867</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45901</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44519</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45377</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45541</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45406</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45554</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45216</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44995</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>45506</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>45919</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45554</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>45919</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>45919</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45180</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>45919</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45401</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45420</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>45504</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>45555</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45014</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45014</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>45547</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45643</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45480</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45198</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45786</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>45443</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45476</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44967</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45527</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45252</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45931</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45931</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44974</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45407</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45170</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45804</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45114</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45156</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>45558</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45770</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45480</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45947</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45947</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>45947</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45947</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45820</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45820</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45744</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>45609</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>45174</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45825</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45825</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45085</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45604</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45827</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45245</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>45832</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45832</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45952</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45958</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45960</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45959</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45832</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44993</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45162</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45610</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45965</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45407</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>45096</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45174</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45537</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45169</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45967</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45967</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45967</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45420</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45177</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>44728</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>44768</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45848</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45973</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45554</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45973</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45973</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45973</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45853</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45531</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45853</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45170</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45306</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45306</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45306</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45975</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45237</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>44974</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45754</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45979</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>44648</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45485</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>44498</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45880</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45532</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45532</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45063</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45063</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45686</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45720</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45532</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>46105</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>46107</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>46107</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>46107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>44859</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>46108</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>45987</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>46108</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>46111</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45771</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45992</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45992</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>46111</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>46111</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>46114</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>46119</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>46122</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45040</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45376</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>46129</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>45058</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>46003</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>46134</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>46134</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>46134</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45048</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45250</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45901</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>46136</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>46009</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>46009</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>44603</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45425</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>45534</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>46140</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46140</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45447</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45111</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45252</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45387</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46037</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>46037</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45114</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>44964</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45390</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45090</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45762</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45617</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45762</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>46142</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>46051</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>46051</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>46051</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>46141</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>46056</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45586</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>46142</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>46142</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>46142</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>46142</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46142</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>46142</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>46150</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>46150</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46154</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>46157</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>46163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>46163</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>46163</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>46163</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>46163</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>46170</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>46170</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>46170</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>46170</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>46170</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>46177</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>46177</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>46178</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>46178</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>46178</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>46182</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>46182</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>46185</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>46185</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>46185</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>46191</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>46190</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>46190</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>46191</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>46190</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>46195</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46197</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>46197</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45686</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>46197</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45393</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>46200</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>46199</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>46200</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>46199</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>46210</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45407</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>46265</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>46268</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46274</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>46199</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>46237</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>46279</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>46282</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>46282</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>46285</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>46244</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>46244</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>46244</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>46244</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>46247</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>46290</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>46289</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>46290</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>46290</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>46290</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>46248</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>46237</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>46253</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>46300</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>46302</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46262</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>46262</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32253,7 +32253,7 @@
         <v>46262</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>46262</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>46262</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>46260</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>46260</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>45435</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45786</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45827</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45853</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45897</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45897</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>45897</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45901</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45915</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>46147</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>46182</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>46199</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>46290</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>46260</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>46262</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>

--- a/Översikt SKINNSKATTEBERG.xlsx
+++ b/Översikt SKINNSKATTEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45343</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45450</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>46253</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>46289</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>44908</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>45974</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>45537</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>46289</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>46254</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>45770</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45390</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45425</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>45574</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>46289</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>45537</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45762</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45755</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44829</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45385</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45232</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>45246</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>46140</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45428</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>46150</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>46170</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>46174</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>45474</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>46185</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>46107</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>46210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>45359</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45568</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>45078</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>46279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45519</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44995</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>46285</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>46285</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>45359</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>45322</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>45099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>46308</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46268</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45832</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45548</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>46107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>44789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>44674</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>44829</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44531</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44741</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>44823</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>44529</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>44529</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>44544</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>44519</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44852</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>44544</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>44852</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45174</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44728</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>44728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>45097</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45058</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>45435</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45237</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>45604</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>45425</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45609</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>45111</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>45244</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45406</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44768</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45506</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>44910</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>45420</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>45637</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>45216</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44974</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45375</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>45250</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45247</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>45434</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>45610</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>45162</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44935</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45686</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45571</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45770</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45406</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45532</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>45527</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>45245</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44603</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45198</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44964</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>44993</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>45447</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45617</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45754</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45534</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45198</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>45617</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45890</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45063</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45063</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>46136</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45897</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45897</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>45897</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45897</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45897</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45897</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45114</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>45586</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>46141</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>46140</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45571</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>45571</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>45237</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45434</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45910</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45910</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45910</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>46142</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>46142</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45915</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45915</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>46142</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>46142</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>45410</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>46142</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>46142</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45901</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>46142</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45919</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45919</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45919</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45919</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>45134</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>45096</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45740</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45407</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45376</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>44974</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>45931</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45931</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>45068</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>46150</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>46150</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45329</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45945</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44903</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45947</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45947</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44648</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45947</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45947</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>46154</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>46157</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>45959</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45958</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44936</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45960</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45965</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>45967</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>45967</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45537</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>45973</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>46163</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45973</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45973</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45975</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46163</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46163</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>46163</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>46163</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45979</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45177</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45771</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45987</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45420</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45992</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45992</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45531</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46170</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45512</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>46170</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>46170</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>46170</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>46170</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>46003</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45604</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>46009</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45901</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>46009</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45407</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44803</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>46037</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>46037</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>46177</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45429</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>46178</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>46178</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>46177</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>46178</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>46182</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>46051</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>46051</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45054</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>46051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>46182</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>46056</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45056</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45390</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46185</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45447</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45485</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>46185</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45555</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>46185</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45387</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45063</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45401</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45156</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>46190</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>46190</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>46190</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>46191</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>46191</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45096</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>45170</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>46195</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>46105</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>46107</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>45558</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>46108</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>46107</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>46108</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>46107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>46111</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>46111</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>46197</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>46197</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45393</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>46111</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45686</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>46114</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>46197</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45720</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>46119</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>46199</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>46122</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>45574</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45574</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>46200</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>46200</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>46199</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>46129</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45082</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>46134</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>46134</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44498</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45128</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>46134</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45169</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45554</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>45085</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>45617</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44965</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45114</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>46210</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45006</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45385</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45401</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>44967</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>45568</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45643</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45407</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
         <v>45435</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44995</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44806</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>44883</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>46199</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>45554</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44519</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>46274</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45156</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45252</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45504</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46279</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45306</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45306</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45306</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>46237</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>45170</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>46282</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>46282</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45744</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45174</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46244</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>46244</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46244</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45555</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>45180</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>46244</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45264</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>46285</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>45520</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44713</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45532</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>45532</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>45554</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45048</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>46289</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>45532</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>46290</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>46290</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>46290</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45114</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>46247</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>46290</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>46248</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>45506</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45170</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45252</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45014</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45014</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45762</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45040</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>46237</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>46253</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>45592</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45777</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45777</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>46300</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>45377</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45541</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44867</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>46302</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>45547</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>46260</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45480</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>46260</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45786</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>46262</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45443</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45527</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45476</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>46262</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>46262</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>46262</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>46262</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>46308</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>46265</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>46308</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>46308</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>46308</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>45804</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>46308</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>46308</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>46268</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45480</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>45820</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45820</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>45825</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>45825</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45827</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45832</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>45832</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45832</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>45848</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45853</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45554</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>45853</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>45880</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45435</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>45786</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45827</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>45853</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>45897</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>45897</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45897</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45901</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>45915</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>46147</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>46182</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>46199</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>46290</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>46260</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>46262</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>

--- a/Översikt SKINNSKATTEBERG.xlsx
+++ b/Översikt SKINNSKATTEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45343</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45450</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>46253</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>46289</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>44908</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>45974</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>45537</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>46289</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>46254</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>45770</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45390</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>46150</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45425</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>45574</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>46289</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>45537</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45762</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45755</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44829</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45385</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45232</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>45246</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45596</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>46140</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45428</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>46150</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>46170</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>46174</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>45474</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>46185</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>46107</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>46210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>45359</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45568</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>45078</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>46279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45519</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44995</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>46285</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>46285</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>45359</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>45322</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>45099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>46308</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46268</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45832</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45548</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>46107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>44789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>44879</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>44674</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>44829</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44531</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44741</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>44823</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>44529</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>44529</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>44544</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>44519</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44852</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>44544</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>44852</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45174</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44728</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>44728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>45097</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45058</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>45435</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45237</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>45604</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>45425</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45609</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>45111</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>45244</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45406</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44768</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45506</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>44910</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>45420</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>45637</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>45216</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44974</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45375</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>45250</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45247</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>45434</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>45610</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>45162</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44935</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45686</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45571</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45770</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45406</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45532</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>45527</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>45245</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44603</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45198</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44964</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>44993</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>45447</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45617</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45754</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45534</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45198</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>45617</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45890</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45063</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45063</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>46136</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45897</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45897</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>45897</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45897</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45897</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45897</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45114</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>45586</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>46141</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>46140</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45571</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>45571</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>45237</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45434</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45910</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45910</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45910</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>46142</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>46142</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45915</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45915</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>46142</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>46142</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>45410</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>46142</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>46142</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45901</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>46142</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45919</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45919</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45919</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45919</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>45134</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>45096</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45740</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45407</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45376</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>44974</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>45931</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45931</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>45068</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>46150</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>46150</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45329</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45945</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44903</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45947</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45947</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44648</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45947</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45947</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>46154</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>46157</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>45959</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45958</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44936</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45960</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45965</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>45967</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>45967</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45537</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>45973</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>46163</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45973</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45973</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45975</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46163</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46163</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>46163</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>46163</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45979</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45177</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45771</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45987</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45420</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45992</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45992</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45531</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46170</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45512</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>46170</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>46170</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>46170</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>46170</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>46003</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45604</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>46009</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45901</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>46009</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45407</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44803</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>46037</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>46037</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>46177</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45429</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>46178</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>46178</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>46177</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>46178</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>46182</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>46051</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>46051</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45054</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>46051</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>46182</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>46056</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45056</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45390</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46185</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45447</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45485</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>46185</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45555</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>46185</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45387</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45063</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45401</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45156</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>46190</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>46190</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>46190</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>46191</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>46191</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45096</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>45170</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>46195</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>46105</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>46107</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>45558</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>46108</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>46107</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>46108</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>46107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>46111</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>46111</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>46197</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>46197</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45393</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>46111</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45686</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>46114</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>46197</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45720</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>46119</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>46199</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>46122</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>45574</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45574</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>46200</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>46200</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>46199</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>46129</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45082</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>46134</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>46134</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44498</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45128</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>46134</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45169</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45554</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>45085</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>45617</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44965</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45114</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>46210</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45006</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45385</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45401</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>44967</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>45568</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45643</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45407</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
         <v>45435</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44995</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44806</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>44883</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>46199</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>45554</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44519</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>46274</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45156</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45252</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45504</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46279</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45306</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45306</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45306</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>46237</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>45170</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>46282</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>46282</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45744</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45174</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46244</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>46244</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46244</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45555</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>45180</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>46244</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45264</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>46285</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>45520</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44713</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45532</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>45532</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>45554</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45048</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>46289</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>45532</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>46290</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>46290</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>46290</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45114</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>46247</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>46290</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>46248</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>45506</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45170</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45252</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45014</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45014</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45762</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45040</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>46237</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>46253</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>45592</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45777</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45777</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>46300</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>45377</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45541</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44867</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>46302</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>45547</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>46260</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45480</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>46260</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45786</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>46262</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45443</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45527</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45476</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>46262</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>46262</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>46262</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>46262</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>46308</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>46265</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>46308</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>46308</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>46308</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>45804</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>46308</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>46308</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>46268</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>45480</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>45820</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45820</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>45825</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>45825</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45827</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45832</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>45832</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45832</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>45848</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45853</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45554</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>45853</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>45880</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45435</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>45786</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45827</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>45853</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>45897</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>45897</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45897</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45901</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>45915</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>46147</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>46182</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>46199</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>46290</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>46260</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>46262</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>

--- a/Översikt SKINNSKATTEBERG.xlsx
+++ b/Översikt SKINNSKATTEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45343</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45450</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>46253</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>46289</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>44908</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>46150</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45974</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46289</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45537</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45985</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>46289</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45574</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>46150</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45770</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>45390</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45762</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45755</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45537</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44829</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45246</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>45322</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45385</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>46170</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>46174</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>46185</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45359</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>46210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45474</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>46279</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>46285</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>46285</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45832</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>46261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>46308</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>46268</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>46140</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>46316</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>46316</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>45359</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45232</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>46150</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>45596</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45568</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>45519</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44995</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45428</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>45099</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45548</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>45832</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>46107</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44879</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>44674</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>44829</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44531</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>44545</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44741</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44544</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>44529</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44519</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44545</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44852</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44544</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44852</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>45048</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45250</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>45244</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45329</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>45890</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45198</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45512</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45897</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45897</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>45897</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>45897</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>45897</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45082</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45897</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44603</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>45425</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45910</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45910</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45910</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45915</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45915</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>46163</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>46163</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>45111</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>46163</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>46163</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>46163</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45919</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45252</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45919</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45919</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45919</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>45387</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45114</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>44964</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>46170</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>46170</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45434</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>46170</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>46170</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>45390</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>45931</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>45931</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>46170</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>45762</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45762</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45435</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45435</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45637</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>46177</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>45945</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45006</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>45410</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>44806</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>46177</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>45447</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45947</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>45947</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45947</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45056</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>45947</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>46178</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45520</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>46178</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>46178</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44883</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>44803</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>45952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>44910</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>46182</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>46182</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45134</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45401</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45114</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>46185</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>46185</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45958</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>46185</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45068</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45960</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44713</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45592</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45959</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45571</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>45571</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>45617</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45965</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>45506</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>46191</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>46190</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>46190</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>46191</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>45170</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>46190</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45967</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45967</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45967</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45604</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>46195</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>46197</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>46197</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45973</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44935</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45973</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45686</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45973</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>46197</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45393</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45973</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>46200</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>46199</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>45237</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>45975</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>46200</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>46199</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45979</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45156</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45385</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45571</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45740</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45987</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45771</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45992</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>46210</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45096</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45992</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45097</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45554</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>45617</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45407</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45777</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45777</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>46003</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>44867</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46199</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45901</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45377</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45541</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>45247</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>46009</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>46009</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>46237</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>46279</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>46282</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45547</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>46282</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45480</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45786</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45443</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>46285</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>46037</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>46037</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45476</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45527</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>46244</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>46244</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>46244</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>46244</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>46247</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>46290</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>46051</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>46289</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>46051</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>46051</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45804</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>46290</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>46056</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>46290</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>46290</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45480</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>46248</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45820</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45820</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>46237</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45825</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45825</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45827</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>46253</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45832</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45832</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>45832</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>46300</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>45848</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>46302</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>46105</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>45574</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>45574</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45554</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>46107</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>46107</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>46107</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45853</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45853</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>46108</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>46108</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>46111</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>46111</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>46111</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>46114</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>46119</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>46122</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>46260</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>46260</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>46308</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>46129</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45880</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>46265</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>46262</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>46262</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>46262</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>46134</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46134</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>46134</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>46308</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45054</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>46308</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>46308</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>46308</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>46262</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>46262</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>46308</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>46136</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>45406</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45554</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45216</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>45506</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45554</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45504</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>45534</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45555</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>46140</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>46140</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>45447</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>46268</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46316</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46316</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46316</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>46316</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>46316</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44967</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>46316</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45617</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45252</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>46142</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44974</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>46141</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>46318</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45586</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>46142</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46142</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>46142</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>46142</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>46142</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>46142</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>45156</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>46150</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>46150</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45558</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>46154</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>46157</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45744</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>45609</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>45604</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>44993</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>45162</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45610</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45537</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45177</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>44728</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>44768</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>45531</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45754</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44648</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45485</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>45686</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>45720</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45406</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45264</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45063</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>44903</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>45555</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45128</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45375</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44965</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45568</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44936</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>45527</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>45434</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45429</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44519</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>44995</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45180</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45401</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45420</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45014</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45014</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45643</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45198</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>45407</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45170</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45114</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45770</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45174</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45085</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45245</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>44728</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>45407</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>45096</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45174</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45169</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>45420</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45170</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45306</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45306</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45306</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45237</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44498</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45532</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45532</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>45063</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45063</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45532</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>44859</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45040</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45376</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>45058</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45435</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45786</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45827</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45853</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45897</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45897</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>45897</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45901</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45915</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>46147</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46182</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>46199</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>46290</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>46260</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>46262</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>

--- a/Översikt SKINNSKATTEBERG.xlsx
+++ b/Översikt SKINNSKATTEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45343</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45450</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>46253</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>46289</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>44908</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>46150</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>45974</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46289</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45537</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45985</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>46289</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45574</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>46150</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45770</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>45390</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45762</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45755</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45537</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44829</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45246</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>45322</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45385</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>46170</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>46174</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>46185</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45359</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>46210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45474</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>46279</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>46285</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>46285</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45832</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>46261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>46308</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>46268</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>46140</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>46316</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>46316</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>45359</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45232</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>46150</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>45596</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45568</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>45519</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44995</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45428</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>45099</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45548</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>45832</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>46107</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44879</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>44674</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>44829</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44531</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>44545</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44741</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44544</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>44529</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44519</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44545</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44852</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44544</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>44852</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>45048</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45250</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>45244</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45329</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>45890</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45198</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45512</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45897</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45897</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>45897</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>45897</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>45897</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45082</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45897</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44603</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>45425</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45910</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45910</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45910</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45915</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45915</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>46163</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>46163</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>45111</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>46163</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>46163</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>46163</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45919</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45252</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45919</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45919</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45919</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>45387</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45114</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>44964</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>46170</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>46170</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45434</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>46170</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>46170</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>45390</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>45931</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>45931</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>46170</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>45762</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45762</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45435</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45435</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45637</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>46177</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>45945</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45006</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>45410</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>44806</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>46177</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>45447</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45947</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>45947</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45947</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45056</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>45947</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>46178</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45520</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>46178</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>46178</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44883</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>44803</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>45952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>44910</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>46182</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>46182</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45134</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45401</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45114</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>46185</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>46185</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45958</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>46185</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45068</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45960</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44713</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45592</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45959</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45571</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>45571</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>45617</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45965</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>45506</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>46191</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>46190</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>46190</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>46191</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>45170</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>46190</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45967</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45967</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45967</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45604</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>46195</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>46197</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>46197</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45973</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44935</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45973</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45686</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45973</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>46197</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45393</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45973</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>46200</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>46199</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>45237</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>45975</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>46200</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>46199</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45979</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45156</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45385</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45571</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45740</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45987</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45771</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45992</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>46210</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45096</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45992</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45097</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45554</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>45617</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45407</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45777</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45777</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>46003</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>44867</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46199</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45901</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45377</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45541</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>45247</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>46009</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>46009</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>46237</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>46279</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>46282</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45547</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>46282</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45480</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45786</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45443</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>46285</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>46037</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>46037</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45476</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45527</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>46244</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>46244</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>46244</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>46244</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>46247</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>46290</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>46051</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>46289</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>46051</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>46051</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45804</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>46290</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>46056</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>46290</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>46290</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45480</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>46248</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45820</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45820</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>46237</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45825</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45825</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45827</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>46253</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45832</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45832</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>45832</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>46300</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>45848</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>46302</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>46105</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>45574</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>45574</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45554</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>46107</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>46107</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>46107</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45853</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45853</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>46108</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>46108</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>46111</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>46111</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>46111</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>46114</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>46119</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>46122</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>46260</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>46260</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>46308</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>46129</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45880</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>46265</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>46262</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>46262</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>46262</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>46134</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46134</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>46134</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>46308</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45054</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>46308</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>46308</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>46308</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>46262</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>46262</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>46308</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>46136</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>45406</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45554</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45216</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>45506</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45554</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45504</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>45534</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45555</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>46140</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>46140</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>45447</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>46268</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46316</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46316</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46316</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>46316</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>46316</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44967</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>46316</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45617</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45252</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>46142</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>44974</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>46141</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>46318</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45586</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>46142</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46142</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>46142</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>46142</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>46142</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>46142</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>45156</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>46150</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>46150</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45558</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>46154</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>46157</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45744</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>45609</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>45604</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>44993</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>45162</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45610</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45537</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45177</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>44728</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>44768</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>45531</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45754</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44648</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45485</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>45686</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>45720</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45406</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45264</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45063</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>44903</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>45555</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45128</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45375</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44965</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45568</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44936</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>45527</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>45434</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45429</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44519</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>44995</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45180</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45401</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45420</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45014</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45014</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45643</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45198</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>45407</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45170</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45114</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45770</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45174</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45085</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45245</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>44728</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>45407</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>45096</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45174</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45169</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>45420</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45170</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45306</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45306</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45306</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45237</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44498</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45532</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45532</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>45063</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45063</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45532</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>44859</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45040</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45376</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>45058</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45435</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45786</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45827</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45853</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45897</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45897</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>45897</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45901</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45915</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>46147</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46182</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>46199</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>46290</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>46260</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>46262</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
